--- a/parafit_summary_switch.xlsx
+++ b/parafit_summary_switch.xlsx
@@ -476,10 +476,10 @@
         <v>148</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>5.41</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         <v>490</v>
       </c>
       <c r="E3" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F3" t="n">
-        <v>23.67</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="4">
@@ -520,10 +520,10 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>60.87</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="5">
